--- a/templates/bungalow_15m2.xlsx
+++ b/templates/bungalow_15m2.xlsx
@@ -596,6 +596,18 @@
       </c>
       <c r="E18" s="3" t="n"/>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Fonction</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>BUREAU / SALLE DE REUNION / VESTIAIRE / REFECTOIRE</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>

--- a/templates/bungalow_15m2.xlsx
+++ b/templates/bungalow_15m2.xlsx
@@ -2,42 +2,146 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="12660" tabRatio="600" firstSheet="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Etat des lieux" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="bungalow" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="125725" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+  <fonts count="21">
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial Black"/>
+      <family val="2"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color indexed="12"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <name val="Arial Black"/>
+      <family val="2"/>
+      <i val="1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
-    </font>
-    <font>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="16"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
       <i val="1"/>
-      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="18"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -46,16 +150,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EFEFEF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -64,34 +164,597 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -166,7 +829,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -443,7 +1106,70 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1" cy="1"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </a:spPr>
+      <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="0" rIns="0" bIns="0" upright="1"/>
+      <a:lstStyle/>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1" cy="1"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="none" w="med" len="med"/>
+        </a:ln>
+        <a:effectLst/>
+      </a:spPr>
+      <a:bodyPr vertOverflow="clip" wrap="square" lIns="18288" tIns="0" rIns="0" bIns="0" upright="1"/>
+      <a:lstStyle/>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -454,168 +1180,619 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12.85546875" customWidth="1" style="58" min="2" max="2"/>
+    <col width="14.42578125" customWidth="1" style="58" min="6" max="6"/>
+    <col width="12.28515625" customWidth="1" style="58" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ÉTAT DES LIEUX — bungalow_15m2.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Chantier</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Adresse</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Code postal</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Ville</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
+    <row r="1">
+      <c r="E1" s="89" t="inlineStr">
+        <is>
+          <t>ETAT DES LIEUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="15" customHeight="1" s="58">
+      <c r="E5" s="92" t="inlineStr">
+        <is>
+          <t>Client : …………………………………………………</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="58">
+      <c r="A6" s="91" t="inlineStr">
+        <is>
+          <t>Bungalow n° : A …………………………….</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="92" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="58">
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>Chantier : ………………………………………………</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="58">
+      <c r="E8" s="92" t="n"/>
+      <c r="F8" s="92" t="n"/>
+      <c r="G8" s="92" t="n"/>
+      <c r="H8" s="92" t="n"/>
     </row>
     <row r="9">
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>MOBILIER</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Qté</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n"/>
-    </row>
-    <row r="11">
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Chaise</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Banc</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n"/>
-    </row>
-    <row r="13">
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Armoire</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Fauteuil</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Caisson</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Refrigerateur</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Micro Ondes</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Evier</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n"/>
+      <c r="A9" s="93" t="inlineStr">
+        <is>
+          <t>BUREAU      /      SALLE DE REUNION    /     VESTIAIRE         /    REFECTOIRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="58">
+      <c r="A10" s="93" t="inlineStr">
+        <is>
+          <t>CLIMATISE :      OUI          NON</t>
+        </is>
+      </c>
+      <c r="D10" s="93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   CLEF :         OUI                 NON</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="58" thickBot="1">
+      <c r="A11" s="93" t="n"/>
+      <c r="B11" s="93" t="n"/>
+      <c r="C11" s="93" t="n"/>
+      <c r="D11" s="93" t="inlineStr">
+        <is>
+          <t>AVEC CROCHET / SANS CROCHET</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20.25" customHeight="1" s="58" thickBot="1">
+      <c r="A12" s="154" t="inlineStr">
+        <is>
+          <t>ETAT EXTERIEUR</t>
+        </is>
+      </c>
+      <c r="B12" s="80" t="n"/>
+      <c r="C12" s="80" t="n"/>
+      <c r="D12" s="80" t="n"/>
+      <c r="E12" s="80" t="n"/>
+      <c r="F12" s="80" t="n"/>
+      <c r="G12" s="80" t="n"/>
+      <c r="H12" s="81" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Fonction</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>BUREAU / SALLE DE REUNION / VESTIAIRE / REFECTOIRE</t>
-        </is>
-      </c>
+      <c r="A20" s="97" t="n"/>
+      <c r="B20" s="97" t="n"/>
+      <c r="D20" s="97" t="n"/>
+      <c r="E20" s="97" t="n"/>
+      <c r="G20" s="97" t="n"/>
+      <c r="H20" s="97" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="97" t="n"/>
+      <c r="B21" s="97" t="n"/>
+      <c r="D21" s="97" t="n"/>
+      <c r="E21" s="97" t="n"/>
+      <c r="G21" s="97" t="n"/>
+      <c r="H21" s="97" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>État réel / Réserves / Signatures — NON pré-rempli (rempli à la main)</t>
-        </is>
-      </c>
+      <c r="A22" s="97" t="n"/>
+      <c r="B22" s="97" t="n"/>
+      <c r="D22" s="97" t="n"/>
+      <c r="E22" s="97" t="n"/>
+      <c r="G22" s="97" t="n"/>
+      <c r="H22" s="97" t="n"/>
+    </row>
+    <row r="23" ht="19.5" customHeight="1" s="58" thickBot="1">
+      <c r="A23" s="97" t="n"/>
+      <c r="B23" s="97" t="inlineStr">
+        <is>
+          <t>Longpan AV</t>
+        </is>
+      </c>
+      <c r="D23" s="97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Pignon D</t>
+        </is>
+      </c>
+      <c r="E23" s="97" t="n"/>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Longpan AR</t>
+        </is>
+      </c>
+      <c r="G23" s="97" t="n"/>
+      <c r="H23" s="97" t="inlineStr">
+        <is>
+          <t>Pignon G</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="58" thickBot="1">
+      <c r="A24" s="155" t="inlineStr">
+        <is>
+          <t>Légende</t>
+        </is>
+      </c>
+      <c r="B24" s="81" t="n"/>
+      <c r="C24" s="156" t="inlineStr">
+        <is>
+          <t>Enfoncement :      x</t>
+        </is>
+      </c>
+      <c r="D24" s="81" t="n"/>
+      <c r="E24" s="156" t="inlineStr">
+        <is>
+          <t>Rayure :      /</t>
+        </is>
+      </c>
+      <c r="F24" s="81" t="n"/>
+      <c r="G24" s="156" t="inlineStr">
+        <is>
+          <t>Trou :      o</t>
+        </is>
+      </c>
+      <c r="H24" s="81" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="58" thickBot="1">
+      <c r="C25" s="157" t="inlineStr">
+        <is>
+          <t>Début de loc</t>
+        </is>
+      </c>
+      <c r="D25" s="80" t="n"/>
+      <c r="E25" s="81" t="n"/>
+      <c r="F25" s="157" t="inlineStr">
+        <is>
+          <t>Fin de loc</t>
+        </is>
+      </c>
+      <c r="G25" s="80" t="n"/>
+      <c r="H25" s="81" t="n"/>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" s="58" thickBot="1">
+      <c r="A26" s="158" t="inlineStr">
+        <is>
+          <t>Panneaux</t>
+        </is>
+      </c>
+      <c r="B26" s="81" t="n"/>
+      <c r="C26" s="159" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="D26" s="66" t="n"/>
+      <c r="E26" s="67" t="n"/>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="G26" s="66" t="n"/>
+      <c r="H26" s="67" t="n"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" s="58" thickBot="1">
+      <c r="A27" s="158" t="inlineStr">
+        <is>
+          <t>Porte + butoir</t>
+        </is>
+      </c>
+      <c r="B27" s="81" t="n"/>
+      <c r="C27" s="160" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="D27" s="80" t="n"/>
+      <c r="E27" s="81" t="n"/>
+      <c r="F27" s="81" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="G27" s="80" t="n"/>
+      <c r="H27" s="81" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="58" thickBot="1">
+      <c r="A28" s="158" t="inlineStr">
+        <is>
+          <t>Coffret électrique</t>
+        </is>
+      </c>
+      <c r="B28" s="81" t="n"/>
+      <c r="C28" s="160" t="n"/>
+      <c r="D28" s="80" t="n"/>
+      <c r="E28" s="81" t="n"/>
+      <c r="F28" s="81" t="n"/>
+      <c r="G28" s="80" t="n"/>
+      <c r="H28" s="81" t="n"/>
+    </row>
+    <row r="29" ht="8.25" customHeight="1" s="58" thickBot="1">
+      <c r="A29" s="18" t="n"/>
+      <c r="B29" s="103" t="n"/>
+    </row>
+    <row r="30" ht="20.25" customHeight="1" s="58" thickBot="1">
+      <c r="A30" s="154" t="inlineStr">
+        <is>
+          <t>ETAT INTERIEUR</t>
+        </is>
+      </c>
+      <c r="B30" s="80" t="n"/>
+      <c r="C30" s="80" t="n"/>
+      <c r="D30" s="80" t="n"/>
+      <c r="E30" s="80" t="n"/>
+      <c r="F30" s="80" t="n"/>
+      <c r="G30" s="80" t="n"/>
+      <c r="H30" s="81" t="n"/>
+    </row>
+    <row r="31" ht="17.25" customHeight="1" s="58" thickBot="1">
+      <c r="C31" s="157" t="inlineStr">
+        <is>
+          <t>Début de loc</t>
+        </is>
+      </c>
+      <c r="D31" s="80" t="n"/>
+      <c r="E31" s="81" t="n"/>
+      <c r="F31" s="157" t="inlineStr">
+        <is>
+          <t>Fin de loc</t>
+        </is>
+      </c>
+      <c r="G31" s="80" t="n"/>
+      <c r="H31" s="81" t="n"/>
+    </row>
+    <row r="32" ht="27" customHeight="1" s="58">
+      <c r="A32" s="158" t="inlineStr">
+        <is>
+          <t>Panneaux</t>
+        </is>
+      </c>
+      <c r="B32" s="67" t="n"/>
+      <c r="C32" s="159" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="D32" s="66" t="n"/>
+      <c r="E32" s="67" t="n"/>
+      <c r="F32" s="67" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="G32" s="66" t="n"/>
+      <c r="H32" s="67" t="n"/>
+    </row>
+    <row r="33" ht="27" customHeight="1" s="58">
+      <c r="A33" s="57" t="n"/>
+      <c r="B33" s="98" t="n"/>
+      <c r="C33" s="161" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="E33" s="98" t="n"/>
+      <c r="F33" s="98" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="H33" s="98" t="n"/>
+    </row>
+    <row r="34" ht="27" customHeight="1" s="58" thickBot="1">
+      <c r="A34" s="60" t="n"/>
+      <c r="B34" s="109" t="n"/>
+      <c r="C34" s="162" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="D34" s="61" t="n"/>
+      <c r="E34" s="109" t="n"/>
+      <c r="F34" s="109" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="G34" s="61" t="n"/>
+      <c r="H34" s="109" t="n"/>
+    </row>
+    <row r="35" ht="27" customHeight="1" s="58">
+      <c r="A35" s="163" t="inlineStr">
+        <is>
+          <t>Sol</t>
+        </is>
+      </c>
+      <c r="B35" s="67" t="n"/>
+      <c r="C35" s="159" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="D35" s="66" t="n"/>
+      <c r="E35" s="67" t="n"/>
+      <c r="F35" s="159" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="G35" s="66" t="n"/>
+      <c r="H35" s="67" t="n"/>
+    </row>
+    <row r="36" ht="27" customHeight="1" s="58">
+      <c r="A36" s="164" t="inlineStr">
+        <is>
+          <t>Interrupteur</t>
+        </is>
+      </c>
+      <c r="B36" s="98" t="n"/>
+      <c r="C36" s="161" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="E36" s="98" t="n"/>
+      <c r="F36" s="161" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="H36" s="98" t="n"/>
+    </row>
+    <row r="37" ht="27" customHeight="1" s="58">
+      <c r="A37" s="164" t="inlineStr">
+        <is>
+          <t>Luminaire</t>
+        </is>
+      </c>
+      <c r="B37" s="98" t="n"/>
+      <c r="C37" s="161" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="E37" s="98" t="n"/>
+      <c r="F37" s="161" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="H37" s="98" t="n"/>
+    </row>
+    <row r="38" ht="27" customHeight="1" s="58">
+      <c r="A38" s="164" t="inlineStr">
+        <is>
+          <t>Prises électriques</t>
+        </is>
+      </c>
+      <c r="B38" s="98" t="n"/>
+      <c r="C38" s="161" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="E38" s="98" t="n"/>
+      <c r="F38" s="161" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="H38" s="98" t="n"/>
+    </row>
+    <row r="39" ht="27" customHeight="1" s="58">
+      <c r="A39" s="55" t="inlineStr">
+        <is>
+          <t>Prise téléphonique</t>
+        </is>
+      </c>
+      <c r="B39" s="56" t="n"/>
+      <c r="C39" s="161" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="E39" s="98" t="n"/>
+      <c r="F39" s="161" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="H39" s="98" t="n"/>
+    </row>
+    <row r="40" ht="27" customHeight="1" s="58">
+      <c r="A40" s="55" t="inlineStr">
+        <is>
+          <t>Radiateur</t>
+        </is>
+      </c>
+      <c r="B40" s="56" t="n"/>
+      <c r="C40" s="161" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="E40" s="98" t="n"/>
+      <c r="F40" s="161" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="H40" s="98" t="n"/>
+    </row>
+    <row r="41" ht="27" customHeight="1" s="58">
+      <c r="A41" s="164" t="inlineStr">
+        <is>
+          <t>Fenêtre + Volet</t>
+        </is>
+      </c>
+      <c r="B41" s="98" t="n"/>
+      <c r="C41" s="161" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="E41" s="98" t="n"/>
+      <c r="F41" s="161" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="H41" s="98" t="n"/>
+    </row>
+    <row r="42" ht="27" customHeight="1" s="58" thickBot="1">
+      <c r="A42" s="164" t="inlineStr">
+        <is>
+          <t>Divers</t>
+        </is>
+      </c>
+      <c r="B42" s="98" t="n"/>
+      <c r="C42" s="161" t="inlineStr">
+        <is>
+          <t>………………………………………………</t>
+        </is>
+      </c>
+      <c r="E42" s="98" t="n"/>
+      <c r="F42" s="162" t="inlineStr">
+        <is>
+          <t>…………………………………………………..</t>
+        </is>
+      </c>
+      <c r="G42" s="61" t="n"/>
+      <c r="H42" s="109" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="58" thickBot="1">
+      <c r="A43" s="165" t="inlineStr">
+        <is>
+          <t>MATERIEL A ASSURER PAR VOS SOINS (VOL, INCENDIE, BRIS DE GLACE, DEGATS DES EAUX.)</t>
+        </is>
+      </c>
+      <c r="B43" s="80" t="n"/>
+      <c r="C43" s="80" t="n"/>
+      <c r="D43" s="80" t="n"/>
+      <c r="E43" s="80" t="n"/>
+      <c r="F43" s="80" t="n"/>
+      <c r="G43" s="80" t="n"/>
+      <c r="H43" s="81" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="93" t="inlineStr">
+        <is>
+          <t>Date, Nom et Signature</t>
+        </is>
+      </c>
+      <c r="E44" s="93" t="inlineStr">
+        <is>
+          <t>Date, Nom et Signature</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="93" t="n"/>
+      <c r="B45" s="93" t="n"/>
+      <c r="C45" s="93" t="n"/>
+      <c r="D45" s="93" t="n"/>
+      <c r="E45" s="93" t="n"/>
+      <c r="F45" s="93" t="n"/>
+      <c r="G45" s="93" t="n"/>
+      <c r="H45" s="93" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="97" t="inlineStr">
+        <is>
+          <t>Signature précédée mention "bon pour accord"</t>
+        </is>
+      </c>
+      <c r="E46" s="97" t="inlineStr">
+        <is>
+          <t>Signature précédée mention "bon pour accord"</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="97" t="n"/>
+      <c r="E48" s="97" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="64">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E1:H4"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="A32:B34"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C25:E25"/>
+  </mergeCells>
+  <pageMargins left="0.16" right="0.15" top="0.16" bottom="0.15" header="0.16" footer="0.15"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>